--- a/05_access_and_privacy/access-decision-log.xlsx
+++ b/05_access_and_privacy/access-decision-log.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\enterprise-data-governance-operating-system\05_access_and_privacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CBE932F-BFC1-4E98-8AA3-4805C49E186E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2C316A-D6C3-4F86-BC80-898032BA601A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{08204615-4595-4556-910A-46E1662AB72C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="1" xr2:uid="{08204615-4595-4556-910A-46E1662AB72C}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
     <sheet name="Decision Log" sheetId="2" r:id="rId2"/>
     <sheet name="Lists" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Log'!$A$1:$W$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,11 +41,311 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="93">
+  <si>
+    <t>Access Decision Log Workbook</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Provides a structured record of significant access requests, exceptions, and sharing decisions.</t>
+  </si>
+  <si>
+    <t>How to use</t>
+  </si>
+  <si>
+    <t>Log material access approvals, exceptions, rejections, temporary approvals, and high-sensitivity sharing cases.</t>
+  </si>
+  <si>
+    <t>Governance rule</t>
+  </si>
+  <si>
+    <t>Use this log for non-routine, sensitive, cross-team, external, or exception-based access decisions.</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Request Type</t>
+  </si>
+  <si>
+    <t>Risk Level</t>
+  </si>
+  <si>
+    <t>Fulfilment Status</t>
+  </si>
+  <si>
+    <t>Request ID</t>
+  </si>
+  <si>
+    <t>Request Date</t>
+  </si>
+  <si>
+    <t>Requester</t>
+  </si>
+  <si>
+    <t>Requester Role / Unit</t>
+  </si>
+  <si>
+    <t>Asset / System</t>
+  </si>
+  <si>
+    <t>Data Asset / Report Name</t>
+  </si>
+  <si>
+    <t>Requested Access / Sharing</t>
+  </si>
+  <si>
+    <t>Business Need</t>
+  </si>
+  <si>
+    <t>Minimum Necessary Checked</t>
+  </si>
+  <si>
+    <t>Sensitive Data Involved</t>
+  </si>
+  <si>
+    <t>Decision Owner</t>
+  </si>
+  <si>
+    <t>Decision Date</t>
+  </si>
+  <si>
+    <t>Conditions / Limitations</t>
+  </si>
+  <si>
+    <t>Review / End Date</t>
+  </si>
+  <si>
+    <t>Fulfilled By</t>
+  </si>
+  <si>
+    <t>Date Fulfilled</t>
+  </si>
+  <si>
+    <t>Related Ticket ID</t>
+  </si>
+  <si>
+    <t>Notes / Rationale</t>
+  </si>
+  <si>
+    <t>ADL-001</t>
+  </si>
+  <si>
+    <t>A. Chen</t>
+  </si>
+  <si>
+    <t>Analytics / Finance</t>
+  </si>
+  <si>
+    <t>Reporting Mart</t>
+  </si>
+  <si>
+    <t>Monthly Finance Detail Mart</t>
+  </si>
+  <si>
+    <t>Confidential</t>
+  </si>
+  <si>
+    <t>New Access</t>
+  </si>
+  <si>
+    <t>Read-only detailed mart access</t>
+  </si>
+  <si>
+    <t>Recurring month-end variance analysis</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Finance Data Owner</t>
+  </si>
+  <si>
+    <t>Approved with Conditions</t>
+  </si>
+  <si>
+    <t>No onward sharing; quarterly review</t>
+  </si>
+  <si>
+    <t>Fulfilled</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>REQ-1042</t>
+  </si>
+  <si>
+    <t>Approved because detailed variance review is required</t>
+  </si>
+  <si>
+    <t>ADL-002</t>
+  </si>
+  <si>
+    <t>M. Patel</t>
+  </si>
+  <si>
+    <t>External Partner</t>
+  </si>
+  <si>
+    <t>Secure Extract Service</t>
+  </si>
+  <si>
+    <t>Approved Claims Extract</t>
+  </si>
+  <si>
+    <t>Restricted</t>
+  </si>
+  <si>
+    <t>External Sharing</t>
+  </si>
+  <si>
+    <t>Approved subset extract</t>
+  </si>
+  <si>
+    <t>Contracted reconciliation support</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Claims Data Owner</t>
+  </si>
+  <si>
+    <t>Time-bound; approved fields only; no redistribution</t>
+  </si>
+  <si>
+    <t>REQ-1091</t>
+  </si>
+  <si>
+    <t>External sharing required elevated review</t>
+  </si>
+  <si>
+    <t>ADL-003</t>
+  </si>
+  <si>
+    <t>R. Singh</t>
+  </si>
+  <si>
+    <t>Operations / Region East</t>
+  </si>
+  <si>
+    <t>Operations Dashboard</t>
+  </si>
+  <si>
+    <t>Regional Service Backlog Dashboard</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>Access Change</t>
+  </si>
+  <si>
+    <t>Expand from local to regional view</t>
+  </si>
+  <si>
+    <t>Regional oversight responsibility expanded</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Regional scope only</t>
+  </si>
+  <si>
+    <t>Dashboard Admin</t>
+  </si>
+  <si>
+    <t>REQ-1174</t>
+  </si>
+  <si>
+    <t>Scope aligned to management role</t>
+  </si>
+  <si>
+    <t>ADL-004</t>
+  </si>
+  <si>
+    <t>J. Brown</t>
+  </si>
+  <si>
+    <t>Analytics / Corporate</t>
+  </si>
+  <si>
+    <t>Customer Master</t>
+  </si>
+  <si>
+    <t>Customer Contact Detail Extract</t>
+  </si>
+  <si>
+    <t>Exception Request</t>
+  </si>
+  <si>
+    <t>Downloadable extract with direct identifiers</t>
+  </si>
+  <si>
+    <t>One-time investigation request</t>
+  </si>
+  <si>
+    <t>Customer Data Owner</t>
+  </si>
+  <si>
+    <t>Escalated</t>
+  </si>
+  <si>
+    <t>Escalated for privacy review</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>REQ-1233</t>
+  </si>
+  <si>
+    <t>Broad identifier access requires stronger review</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +372,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,27 +691,463 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12574E5D-1580-4DB0-B9BA-B3EA1D5F11C8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.9296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="135" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86124E4C-668D-4529-B4A7-74F4A4D89F9E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.06640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.06640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="41.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="44.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="3">
+        <v>46031</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" s="3">
+        <v>46121</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="3">
+        <v>46032</v>
+      </c>
+      <c r="V2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46037</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="3">
+        <v>46038</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="3">
+        <v>46068</v>
+      </c>
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="3">
+        <v>46038</v>
+      </c>
+      <c r="V3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46055</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" s="3">
+        <v>46056</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R4" s="3">
+        <v>46145</v>
+      </c>
+      <c r="S4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" t="s">
+        <v>76</v>
+      </c>
+      <c r="U4" s="3">
+        <v>46056</v>
+      </c>
+      <c r="V4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46073</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" s="3">
+        <v>46074</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>89</v>
+      </c>
+      <c r="R5" s="3">
+        <v>46082</v>
+      </c>
+      <c r="S5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V5" t="s">
+        <v>91</v>
+      </c>
+      <c r="W5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:W5" xr:uid="{86124E4C-668D-4529-B4A7-74F4A4D89F9E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542ABF54-7C0B-437D-8E2D-F7A53A4CF843}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>